--- a/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
+++ b/debug/judgements_q_sty_swi/excel_overviews/gpt-4.1_vs_Llama-3.1-8B-Instruct/Qwen3-4B-Instruct-2507/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="D2">
-        <v>536</v>
+        <v>545</v>
       </c>
       <c r="E2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G2">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="H2">
         <v>852</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="D3">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="E3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H3">
         <v>852</v>
